--- a/update.xlsx
+++ b/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E900F56-237F-4CAC-92EB-1E3443F31BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F254E7-3AB5-47D6-B266-633F256612DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8100" yWindow="-13545" windowWidth="17280" windowHeight="9960" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="14400" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -365,7 +365,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -388,13 +388,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -424,6 +437,12 @@
     </xf>
     <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1268,33 +1287,55 @@
       <c r="A14" s="9">
         <v>46204</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="7"/>
+      <c r="B14" s="6">
+        <v>10978</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="E14" s="6">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F14" s="6">
+        <v>45487</v>
+      </c>
+      <c r="G14" s="6">
+        <v>3438</v>
+      </c>
+      <c r="H14" s="6">
+        <v>43792</v>
+      </c>
+      <c r="I14" s="6">
+        <v>2849</v>
+      </c>
+      <c r="J14" s="6">
+        <v>1695</v>
+      </c>
+      <c r="K14" s="6">
+        <v>589</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0.99199999999999999</v>
+      </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="9">
         <v>46235</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="11"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="9">

--- a/update.xlsx
+++ b/update.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F254E7-3AB5-47D6-B266-633F256612DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DB9BF6-086F-4C8B-A8A1-17751D9367B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1090,7 +1090,7 @@
         <v>634</v>
       </c>
       <c r="L8" s="7">
-        <v>0.99545055471306565</v>
+        <v>0.98099999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1128,7 +1128,7 @@
         <v>566</v>
       </c>
       <c r="L9" s="7">
-        <v>0.9922476692338873</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1166,7 +1166,7 @@
         <v>590</v>
       </c>
       <c r="L10" s="7">
-        <v>0.99484493223580273</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1204,7 +1204,7 @@
         <v>509</v>
       </c>
       <c r="L11" s="7">
-        <v>0.99242424242424243</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1242,7 +1242,7 @@
         <v>529</v>
       </c>
       <c r="L12" s="7">
-        <v>0.99315626169046933</v>
+        <v>0.96099999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1280,7 +1280,7 @@
         <v>573</v>
       </c>
       <c r="L13" s="7">
-        <v>0.99088904605400008</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1318,7 +1318,7 @@
         <v>589</v>
       </c>
       <c r="L14" s="7">
-        <v>0.99199999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="15" spans="1:12">

--- a/update.xlsx
+++ b/update.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DB9BF6-086F-4C8B-A8A1-17751D9367B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F254E7-3AB5-47D6-B266-633F256612DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="14400" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1090,7 +1090,7 @@
         <v>634</v>
       </c>
       <c r="L8" s="7">
-        <v>0.98099999999999998</v>
+        <v>0.99545055471306565</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1128,7 +1128,7 @@
         <v>566</v>
       </c>
       <c r="L9" s="7">
-        <v>0.98</v>
+        <v>0.9922476692338873</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1166,7 +1166,7 @@
         <v>590</v>
       </c>
       <c r="L10" s="7">
-        <v>0.97</v>
+        <v>0.99484493223580273</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1204,7 +1204,7 @@
         <v>509</v>
       </c>
       <c r="L11" s="7">
-        <v>0.97199999999999998</v>
+        <v>0.99242424242424243</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1242,7 +1242,7 @@
         <v>529</v>
       </c>
       <c r="L12" s="7">
-        <v>0.96099999999999997</v>
+        <v>0.99315626169046933</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1280,7 +1280,7 @@
         <v>573</v>
       </c>
       <c r="L13" s="7">
-        <v>0.96</v>
+        <v>0.99088904605400008</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1318,7 +1318,7 @@
         <v>589</v>
       </c>
       <c r="L14" s="7">
-        <v>0.95</v>
+        <v>0.99199999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:12">

--- a/update.xlsx
+++ b/update.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI Transportation KPI Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F254E7-3AB5-47D6-B266-633F256612DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54104099-875A-4D18-A605-C8DA4356617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>月份</t>
   </si>
@@ -252,12 +252,43 @@
       <t>(OTIF)</t>
     </r>
   </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Clinic/Dispensary
+(ORDER)</t>
+  </si>
+  <si>
+    <t>Elderly Home
+(ORDER)</t>
+  </si>
+  <si>
+    <t>Home Delivery
+(ORDER)</t>
+  </si>
+  <si>
+    <t>Hospital
+(ORDER)</t>
+  </si>
+  <si>
+    <t>KA
+(ORDER)</t>
+  </si>
+  <si>
+    <t>Macau
+(ORDER)</t>
+  </si>
+  <si>
+    <t>Self Pick Up
+(ORDER)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -350,8 +381,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,8 +408,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -388,26 +444,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -438,11 +481,26 @@
     <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="10" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -778,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBFB83A-3150-496D-BED3-657404FFAB93}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -787,9 +845,13 @@
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="12" max="12" width="12.21875" customWidth="1"/>
+    <col min="13" max="13" width="1.77734375" style="12" customWidth="1"/>
+    <col min="14" max="14" width="19.5546875" style="13" customWidth="1"/>
+    <col min="15" max="20" width="15.33203125" style="13" customWidth="1"/>
+    <col min="21" max="21" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.8">
+    <row r="1" spans="1:21" ht="28.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -826,8 +888,33 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="11"/>
+      <c r="N1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>45839</v>
       </c>
@@ -864,8 +951,17 @@
       <c r="L2" s="7">
         <v>0.99360148176211827</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="10"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>45870</v>
       </c>
@@ -902,8 +998,17 @@
       <c r="L3" s="7">
         <v>0.99309023592216294</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="10"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>45901</v>
       </c>
@@ -940,8 +1045,17 @@
       <c r="L4" s="7">
         <v>0.98300981183366609</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="10"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>45931</v>
       </c>
@@ -978,8 +1092,17 @@
       <c r="L5" s="7">
         <v>0.99219348559832687</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="10"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>45962</v>
       </c>
@@ -1016,8 +1139,17 @@
       <c r="L6" s="7">
         <v>0.9942355201756794</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="10"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>45992</v>
       </c>
@@ -1054,8 +1186,17 @@
       <c r="L7" s="7">
         <v>0.994276636047009</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7" s="10"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46023</v>
       </c>
@@ -1092,8 +1233,33 @@
       <c r="L8" s="7">
         <v>0.99545055471306565</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8" s="10"/>
+      <c r="N8" s="15">
+        <v>23707</v>
+      </c>
+      <c r="O8" s="15">
+        <v>466</v>
+      </c>
+      <c r="P8" s="15">
+        <v>15044</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>9212</v>
+      </c>
+      <c r="R8" s="15">
+        <v>1087</v>
+      </c>
+      <c r="S8" s="15">
+        <v>402</v>
+      </c>
+      <c r="T8" s="15">
+        <v>198</v>
+      </c>
+      <c r="U8" s="15">
+        <v>50116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="9">
         <v>46054</v>
       </c>
@@ -1130,8 +1296,17 @@
       <c r="L9" s="7">
         <v>0.9922476692338873</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9" s="10"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="9">
         <v>46082</v>
       </c>
@@ -1168,8 +1343,17 @@
       <c r="L10" s="7">
         <v>0.99484493223580273</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10" s="10"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="9">
         <v>46113</v>
       </c>
@@ -1206,8 +1390,33 @@
       <c r="L11" s="7">
         <v>0.99242424242424243</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11" s="10"/>
+      <c r="N11" s="15">
+        <v>21187</v>
+      </c>
+      <c r="O11" s="15">
+        <v>505</v>
+      </c>
+      <c r="P11" s="15">
+        <v>14049</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>8342</v>
+      </c>
+      <c r="R11" s="15">
+        <v>824</v>
+      </c>
+      <c r="S11" s="15">
+        <v>369</v>
+      </c>
+      <c r="T11" s="15">
+        <v>264</v>
+      </c>
+      <c r="U11" s="15">
+        <v>45540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="9">
         <v>46143</v>
       </c>
@@ -1244,8 +1453,33 @@
       <c r="L12" s="7">
         <v>0.99315626169046933</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12" s="10"/>
+      <c r="N12" s="15">
+        <v>20972</v>
+      </c>
+      <c r="O12" s="15">
+        <v>476</v>
+      </c>
+      <c r="P12" s="15">
+        <v>14296</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>8077</v>
+      </c>
+      <c r="R12" s="15">
+        <v>837</v>
+      </c>
+      <c r="S12" s="15">
+        <v>488</v>
+      </c>
+      <c r="T12" s="15">
+        <v>297</v>
+      </c>
+      <c r="U12" s="15">
+        <v>45443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="9">
         <v>46174</v>
       </c>
@@ -1282,8 +1516,33 @@
       <c r="L13" s="7">
         <v>0.99088904605400008</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13" s="10"/>
+      <c r="N13" s="15">
+        <v>21874</v>
+      </c>
+      <c r="O13" s="15">
+        <v>527</v>
+      </c>
+      <c r="P13" s="15">
+        <v>14721</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>9395</v>
+      </c>
+      <c r="R13" s="15">
+        <v>920</v>
+      </c>
+      <c r="S13" s="15">
+        <v>433</v>
+      </c>
+      <c r="T13" s="15">
+        <v>204</v>
+      </c>
+      <c r="U13" s="15">
+        <v>48074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="9">
         <v>46204</v>
       </c>
@@ -1320,24 +1579,42 @@
       <c r="L14" s="7">
         <v>0.99199999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14" s="10"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="9">
         <v>46235</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="11"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="9">
         <v>46266</v>
       </c>
@@ -1352,8 +1629,17 @@
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="10"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="9">
         <v>46296</v>
       </c>
@@ -1368,8 +1654,17 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="10"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="9">
         <v>46327</v>
       </c>
@@ -1384,8 +1679,17 @@
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="7"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18" s="10"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="15"/>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="9">
         <v>46357</v>
       </c>
@@ -1400,6 +1704,15 @@
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="7"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI Transportation KPI Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54104099-875A-4D18-A605-C8DA4356617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2028691-D7EF-43AB-B2F5-FF4B727BAF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
@@ -450,7 +450,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -481,16 +481,13 @@
     <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -846,8 +843,8 @@
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="12" max="12" width="12.21875" customWidth="1"/>
     <col min="13" max="13" width="1.77734375" style="12" customWidth="1"/>
-    <col min="14" max="14" width="19.5546875" style="13" customWidth="1"/>
-    <col min="15" max="20" width="15.33203125" style="13" customWidth="1"/>
+    <col min="14" max="14" width="19.5546875" customWidth="1"/>
+    <col min="15" max="20" width="15.33203125" customWidth="1"/>
     <col min="21" max="21" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -889,28 +886,28 @@
         <v>11</v>
       </c>
       <c r="M1" s="11"/>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="13" t="s">
         <v>12</v>
       </c>
     </row>
@@ -952,14 +949,30 @@
         <v>0.99360148176211827</v>
       </c>
       <c r="M2" s="10"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
+      <c r="N2" s="14">
+        <v>21435</v>
+      </c>
+      <c r="O2" s="14">
+        <v>418</v>
+      </c>
+      <c r="P2" s="14">
+        <v>15236</v>
+      </c>
+      <c r="Q2" s="14">
+        <v>8839</v>
+      </c>
+      <c r="R2" s="14">
+        <v>987</v>
+      </c>
+      <c r="S2" s="14">
+        <v>375</v>
+      </c>
+      <c r="T2" s="14">
+        <v>221</v>
+      </c>
+      <c r="U2" s="14">
+        <v>47511</v>
+      </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="9">
@@ -999,14 +1012,30 @@
         <v>0.99309023592216294</v>
       </c>
       <c r="M3" s="10"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
+      <c r="N3" s="14">
+        <v>21070</v>
+      </c>
+      <c r="O3" s="14">
+        <v>388</v>
+      </c>
+      <c r="P3" s="14">
+        <v>14785</v>
+      </c>
+      <c r="Q3" s="14">
+        <v>8582</v>
+      </c>
+      <c r="R3" s="14">
+        <v>984</v>
+      </c>
+      <c r="S3" s="14">
+        <v>405</v>
+      </c>
+      <c r="T3" s="14">
+        <v>242</v>
+      </c>
+      <c r="U3" s="14">
+        <v>46456</v>
+      </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="9">
@@ -1046,14 +1075,30 @@
         <v>0.98300981183366609</v>
       </c>
       <c r="M4" s="10"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
+      <c r="N4" s="14">
+        <v>21223</v>
+      </c>
+      <c r="O4" s="14">
+        <v>433</v>
+      </c>
+      <c r="P4" s="14">
+        <v>14829</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>9020</v>
+      </c>
+      <c r="R4" s="14">
+        <v>906</v>
+      </c>
+      <c r="S4" s="14">
+        <v>371</v>
+      </c>
+      <c r="T4" s="14">
+        <v>304</v>
+      </c>
+      <c r="U4" s="14">
+        <v>47086</v>
+      </c>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="9">
@@ -1093,14 +1138,30 @@
         <v>0.99219348559832687</v>
       </c>
       <c r="M5" s="10"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
+      <c r="N5" s="14">
+        <v>22139</v>
+      </c>
+      <c r="O5" s="14">
+        <v>462</v>
+      </c>
+      <c r="P5" s="14">
+        <v>14906</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>9120</v>
+      </c>
+      <c r="R5" s="14">
+        <v>1004</v>
+      </c>
+      <c r="S5" s="14">
+        <v>391</v>
+      </c>
+      <c r="T5" s="14">
+        <v>271</v>
+      </c>
+      <c r="U5" s="14">
+        <v>48293</v>
+      </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="9">
@@ -1140,14 +1201,30 @@
         <v>0.9942355201756794</v>
       </c>
       <c r="M6" s="10"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
+      <c r="N6" s="14">
+        <v>22216</v>
+      </c>
+      <c r="O6" s="14">
+        <v>412</v>
+      </c>
+      <c r="P6" s="14">
+        <v>14526</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>8541</v>
+      </c>
+      <c r="R6" s="14">
+        <v>920</v>
+      </c>
+      <c r="S6" s="14">
+        <v>444</v>
+      </c>
+      <c r="T6" s="14">
+        <v>300</v>
+      </c>
+      <c r="U6" s="14">
+        <v>47359</v>
+      </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="9">
@@ -1187,14 +1264,30 @@
         <v>0.994276636047009</v>
       </c>
       <c r="M7" s="10"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
+      <c r="N7" s="14">
+        <v>22127</v>
+      </c>
+      <c r="O7" s="14">
+        <v>449</v>
+      </c>
+      <c r="P7" s="14">
+        <v>15626</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>9278</v>
+      </c>
+      <c r="R7" s="14">
+        <v>968</v>
+      </c>
+      <c r="S7" s="14">
+        <v>417</v>
+      </c>
+      <c r="T7" s="14">
+        <v>232</v>
+      </c>
+      <c r="U7" s="14">
+        <v>49097</v>
+      </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="9">
@@ -1234,28 +1327,28 @@
         <v>0.99545055471306565</v>
       </c>
       <c r="M8" s="10"/>
-      <c r="N8" s="15">
+      <c r="N8" s="14">
         <v>23707</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="14">
         <v>466</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="14">
         <v>15044</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="14">
         <v>9212</v>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="14">
         <v>1087</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="14">
         <v>402</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="14">
         <v>198</v>
       </c>
-      <c r="U8" s="15">
+      <c r="U8" s="14">
         <v>50116</v>
       </c>
     </row>
@@ -1297,14 +1390,30 @@
         <v>0.9922476692338873</v>
       </c>
       <c r="M9" s="10"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
+      <c r="N9" s="14">
+        <v>16936</v>
+      </c>
+      <c r="O9" s="14">
+        <v>374</v>
+      </c>
+      <c r="P9" s="14">
+        <v>13203</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>7612</v>
+      </c>
+      <c r="R9" s="14">
+        <v>762</v>
+      </c>
+      <c r="S9" s="14">
+        <v>367</v>
+      </c>
+      <c r="T9" s="14">
+        <v>218</v>
+      </c>
+      <c r="U9" s="14">
+        <v>39472</v>
+      </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="9">
@@ -1344,14 +1453,30 @@
         <v>0.99484493223580273</v>
       </c>
       <c r="M10" s="10"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
+      <c r="N10" s="14">
+        <v>21620</v>
+      </c>
+      <c r="O10" s="14">
+        <v>439</v>
+      </c>
+      <c r="P10" s="14">
+        <v>15525</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>8866</v>
+      </c>
+      <c r="R10" s="14">
+        <v>952</v>
+      </c>
+      <c r="S10" s="14">
+        <v>442</v>
+      </c>
+      <c r="T10" s="14">
+        <v>264</v>
+      </c>
+      <c r="U10" s="14">
+        <v>48108</v>
+      </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="9">
@@ -1391,28 +1516,28 @@
         <v>0.99242424242424243</v>
       </c>
       <c r="M11" s="10"/>
-      <c r="N11" s="15">
+      <c r="N11" s="14">
         <v>21187</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="14">
         <v>505</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="14">
         <v>14049</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="14">
         <v>8342</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="14">
         <v>824</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="14">
         <v>369</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="14">
         <v>264</v>
       </c>
-      <c r="U11" s="15">
+      <c r="U11" s="14">
         <v>45540</v>
       </c>
     </row>
@@ -1454,28 +1579,28 @@
         <v>0.99315626169046933</v>
       </c>
       <c r="M12" s="10"/>
-      <c r="N12" s="15">
+      <c r="N12" s="14">
         <v>20972</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="14">
         <v>476</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="14">
         <v>14296</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="14">
         <v>8077</v>
       </c>
-      <c r="R12" s="15">
+      <c r="R12" s="14">
         <v>837</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="14">
         <v>488</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="14">
         <v>297</v>
       </c>
-      <c r="U12" s="15">
+      <c r="U12" s="14">
         <v>45443</v>
       </c>
     </row>
@@ -1517,28 +1642,28 @@
         <v>0.99088904605400008</v>
       </c>
       <c r="M13" s="10"/>
-      <c r="N13" s="15">
+      <c r="N13" s="14">
         <v>21874</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="14">
         <v>527</v>
       </c>
-      <c r="P13" s="15">
+      <c r="P13" s="14">
         <v>14721</v>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="14">
         <v>9395</v>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="14">
         <v>920</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="14">
         <v>433</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="14">
         <v>204</v>
       </c>
-      <c r="U13" s="15">
+      <c r="U13" s="14">
         <v>48074</v>
       </c>
     </row>
@@ -1580,14 +1705,14 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="M14" s="10"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="9">
@@ -1605,14 +1730,14 @@
       <c r="K15" s="8"/>
       <c r="L15" s="7"/>
       <c r="M15" s="10"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="9">
@@ -1630,14 +1755,14 @@
       <c r="K16" s="8"/>
       <c r="L16" s="7"/>
       <c r="M16" s="10"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="9">
@@ -1655,14 +1780,14 @@
       <c r="K17" s="8"/>
       <c r="L17" s="7"/>
       <c r="M17" s="10"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="9">
@@ -1680,14 +1805,14 @@
       <c r="K18" s="8"/>
       <c r="L18" s="7"/>
       <c r="M18" s="10"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="14"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="9">
@@ -1705,14 +1830,14 @@
       <c r="K19" s="8"/>
       <c r="L19" s="7"/>
       <c r="M19" s="10"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="15"/>
+      <c r="U19" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI Transportation KPI Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2028691-D7EF-43AB-B2F5-FF4B727BAF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B65E120-A6FC-40D8-B8B6-076E908502CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-30" yWindow="-16335" windowWidth="29070" windowHeight="15750" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -256,10 +256,6 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Clinic/Dispensary
-(ORDER)</t>
-  </si>
-  <si>
     <t>Elderly Home
 (ORDER)</t>
   </si>
@@ -281,6 +277,10 @@
   </si>
   <si>
     <t>Self Pick Up
+(ORDER)</t>
+  </si>
+  <si>
+    <t>Clinic/Dispensary/Optical Store
 (ORDER)</t>
   </si>
 </sst>
@@ -843,12 +843,12 @@
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="12" max="12" width="12.21875" customWidth="1"/>
     <col min="13" max="13" width="1.77734375" style="12" customWidth="1"/>
-    <col min="14" max="14" width="19.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.21875" customWidth="1"/>
     <col min="15" max="20" width="15.33203125" customWidth="1"/>
     <col min="21" max="21" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="28.8">
+    <row r="1" spans="1:21" ht="43.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,25 +887,25 @@
       </c>
       <c r="M1" s="11"/>
       <c r="N1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="R1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>19</v>
       </c>
       <c r="U1" s="13" t="s">
         <v>12</v>

--- a/update.xlsx
+++ b/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI Transportation KPI Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B65E120-A6FC-40D8-B8B6-076E908502CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EBCB28-0374-41D1-918E-822C3DE950C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16335" windowWidth="29070" windowHeight="15750" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -971,6 +971,7 @@
         <v>221</v>
       </c>
       <c r="U2" s="14">
+        <f>SUM(N2:T2)</f>
         <v>47511</v>
       </c>
     </row>
@@ -1034,6 +1035,7 @@
         <v>242</v>
       </c>
       <c r="U3" s="14">
+        <f t="shared" ref="U3:U13" si="0">SUM(N3:T3)</f>
         <v>46456</v>
       </c>
     </row>
@@ -1097,6 +1099,7 @@
         <v>304</v>
       </c>
       <c r="U4" s="14">
+        <f t="shared" si="0"/>
         <v>47086</v>
       </c>
     </row>
@@ -1160,6 +1163,7 @@
         <v>271</v>
       </c>
       <c r="U5" s="14">
+        <f t="shared" si="0"/>
         <v>48293</v>
       </c>
     </row>
@@ -1223,6 +1227,7 @@
         <v>300</v>
       </c>
       <c r="U6" s="14">
+        <f t="shared" si="0"/>
         <v>47359</v>
       </c>
     </row>
@@ -1286,6 +1291,7 @@
         <v>232</v>
       </c>
       <c r="U7" s="14">
+        <f t="shared" si="0"/>
         <v>49097</v>
       </c>
     </row>
@@ -1328,7 +1334,8 @@
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="14">
-        <v>23707</v>
+        <f>23707+9844</f>
+        <v>33551</v>
       </c>
       <c r="O8" s="14">
         <v>466</v>
@@ -1349,7 +1356,8 @@
         <v>198</v>
       </c>
       <c r="U8" s="14">
-        <v>50116</v>
+        <f t="shared" si="0"/>
+        <v>59960</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1391,7 +1399,8 @@
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="14">
-        <v>16936</v>
+        <f>16936+7764</f>
+        <v>24700</v>
       </c>
       <c r="O9" s="14">
         <v>374</v>
@@ -1412,7 +1421,8 @@
         <v>218</v>
       </c>
       <c r="U9" s="14">
-        <v>39472</v>
+        <f t="shared" si="0"/>
+        <v>47236</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1454,7 +1464,8 @@
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="14">
-        <v>21620</v>
+        <f>21620+9596</f>
+        <v>31216</v>
       </c>
       <c r="O10" s="14">
         <v>439</v>
@@ -1475,7 +1486,8 @@
         <v>264</v>
       </c>
       <c r="U10" s="14">
-        <v>48108</v>
+        <f t="shared" si="0"/>
+        <v>57704</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1517,7 +1529,8 @@
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="14">
-        <v>21187</v>
+        <f>21187+8201</f>
+        <v>29388</v>
       </c>
       <c r="O11" s="14">
         <v>505</v>
@@ -1538,7 +1551,8 @@
         <v>264</v>
       </c>
       <c r="U11" s="14">
-        <v>45540</v>
+        <f t="shared" si="0"/>
+        <v>53741</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1580,7 +1594,8 @@
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="14">
-        <v>20972</v>
+        <f>20972+8220</f>
+        <v>29192</v>
       </c>
       <c r="O12" s="14">
         <v>476</v>
@@ -1601,7 +1616,8 @@
         <v>297</v>
       </c>
       <c r="U12" s="14">
-        <v>45443</v>
+        <f t="shared" si="0"/>
+        <v>53663</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1643,7 +1659,8 @@
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="14">
-        <v>21874</v>
+        <f>21874+9405</f>
+        <v>31279</v>
       </c>
       <c r="O13" s="14">
         <v>527</v>
@@ -1664,7 +1681,8 @@
         <v>204</v>
       </c>
       <c r="U13" s="14">
-        <v>48074</v>
+        <f t="shared" si="0"/>
+        <v>57479</v>
       </c>
     </row>
     <row r="14" spans="1:21">

--- a/update.xlsx
+++ b/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI Transportation KPI Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EBCB28-0374-41D1-918E-822C3DE950C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4EF828-CC9C-4AB4-AACE-704CE7CD7815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -288,7 +288,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -394,6 +397,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -445,12 +456,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -499,9 +511,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -833,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBFB83A-3150-496D-BED3-657404FFAB93}">
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -841,6 +860,7 @@
     <col min="3" max="3" width="13.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.21875" customWidth="1"/>
     <col min="13" max="13" width="1.77734375" style="12" customWidth="1"/>
     <col min="14" max="14" width="17.21875" customWidth="1"/>
@@ -848,7 +868,7 @@
     <col min="21" max="21" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="43.2">
+    <row r="1" spans="1:23" ht="43.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,7 +931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" s="9">
         <v>45839</v>
       </c>
@@ -975,7 +995,7 @@
         <v>47511</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:23">
       <c r="A3" s="9">
         <v>45870</v>
       </c>
@@ -1039,7 +1059,7 @@
         <v>46456</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:23">
       <c r="A4" s="9">
         <v>45901</v>
       </c>
@@ -1103,7 +1123,7 @@
         <v>47086</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:23">
       <c r="A5" s="9">
         <v>45931</v>
       </c>
@@ -1167,7 +1187,7 @@
         <v>48293</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:23">
       <c r="A6" s="9">
         <v>45962</v>
       </c>
@@ -1231,7 +1251,7 @@
         <v>47359</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:23">
       <c r="A7" s="9">
         <v>45992</v>
       </c>
@@ -1295,7 +1315,7 @@
         <v>49097</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:23">
       <c r="A8" s="9">
         <v>46023</v>
       </c>
@@ -1360,7 +1380,7 @@
         <v>59960</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:23">
       <c r="A9" s="9">
         <v>46054</v>
       </c>
@@ -1425,7 +1445,7 @@
         <v>47236</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:23">
       <c r="A10" s="9">
         <v>46082</v>
       </c>
@@ -1490,7 +1510,7 @@
         <v>57704</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:23">
       <c r="A11" s="9">
         <v>46113</v>
       </c>
@@ -1555,7 +1575,7 @@
         <v>53741</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:23">
       <c r="A12" s="9">
         <v>46143</v>
       </c>
@@ -1620,7 +1640,7 @@
         <v>53663</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:23">
       <c r="A13" s="9">
         <v>46174</v>
       </c>
@@ -1684,8 +1704,9 @@
         <f t="shared" si="0"/>
         <v>57479</v>
       </c>
+      <c r="W13" s="17"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:23">
       <c r="A14" s="9">
         <v>46204</v>
       </c>
@@ -1723,16 +1744,33 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="M14" s="10"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
+      <c r="N14" s="14">
+        <v>40000</v>
+      </c>
+      <c r="O14" s="14">
+        <v>527</v>
+      </c>
+      <c r="P14" s="14">
+        <v>14721</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>9395</v>
+      </c>
+      <c r="R14" s="14">
+        <v>920</v>
+      </c>
+      <c r="S14" s="14">
+        <v>433</v>
+      </c>
+      <c r="T14" s="14">
+        <v>204</v>
+      </c>
+      <c r="U14" s="14">
+        <f t="shared" ref="U14" si="1">SUM(N14:T14)</f>
+        <v>66200</v>
+      </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:23">
       <c r="A15" s="9">
         <v>46235</v>
       </c>
@@ -1757,7 +1795,7 @@
       <c r="T15" s="14"/>
       <c r="U15" s="14"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:23">
       <c r="A16" s="9">
         <v>46266</v>
       </c>
@@ -1857,6 +1895,9 @@
       <c r="T19" s="15"/>
       <c r="U19" s="14"/>
     </row>
+    <row r="23" spans="1:21">
+      <c r="H23" s="16"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI Transportation KPI Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4EF828-CC9C-4AB4-AACE-704CE7CD7815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8120F8CA-46F8-4ACE-966A-BDABE89BFEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
@@ -1710,65 +1710,26 @@
       <c r="A14" s="9">
         <v>46204</v>
       </c>
-      <c r="B14" s="6">
-        <v>10978</v>
-      </c>
-      <c r="C14" s="6">
-        <v>4.2</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="E14" s="6">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F14" s="6">
-        <v>45487</v>
-      </c>
-      <c r="G14" s="6">
-        <v>3438</v>
-      </c>
-      <c r="H14" s="6">
-        <v>43792</v>
-      </c>
-      <c r="I14" s="6">
-        <v>2849</v>
-      </c>
-      <c r="J14" s="6">
-        <v>1695</v>
-      </c>
-      <c r="K14" s="6">
-        <v>589</v>
-      </c>
-      <c r="L14" s="7">
-        <v>0.99199999999999999</v>
-      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="7"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="14">
-        <v>40000</v>
-      </c>
-      <c r="O14" s="14">
-        <v>527</v>
-      </c>
-      <c r="P14" s="14">
-        <v>14721</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>9395</v>
-      </c>
-      <c r="R14" s="14">
-        <v>920</v>
-      </c>
-      <c r="S14" s="14">
-        <v>433</v>
-      </c>
-      <c r="T14" s="14">
-        <v>204</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" ref="U14" si="1">SUM(N14:T14)</f>
-        <v>66200</v>
-      </c>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="9">
